--- a/Workshop week 4.xlsx
+++ b/Workshop week 4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\working\waccache\DM3PEPF00013DD1\EXCELCNV\fe4a3ad8-6478-4e4e-b911-e2835e8e45a9\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssrin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="299" documentId="8_{FD25D4D3-F64E-4313-8E51-203CBEAE246F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE1A8A16-8E4F-41DB-9238-37FC6AF1BB71}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB021E70-EC1F-4132-8B12-3C332C1BCB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" xr2:uid="{1977BA7A-3BD1-4CBB-967F-34529ED38CDE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{1977BA7A-3BD1-4CBB-967F-34529ED38CDE}"/>
   </bookViews>
   <sheets>
     <sheet name="Data source 1" sheetId="4" r:id="rId1"/>
@@ -22,7 +22,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="1296" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2831,9 +2831,8 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2845,7 +2844,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="34" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="20" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2904,14 +2902,14 @@
   </cellStyles>
   <dxfs count="2">
     <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2940,7 +2938,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[A.xlsx]Data source 1!PivotTable1</c:name>
+    <c:name>[Workshop week 4.xlsx]Data source 1!PivotTable1</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -3013,19 +3011,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="5"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3440,7 +3426,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[A.xlsx]Data source 1!PivotTable2</c:name>
+    <c:name>[Workshop week 4.xlsx]Data source 1!PivotTable2</c:name>
     <c:fmtId val="1"/>
   </c:pivotSource>
   <c:chart>
@@ -3513,19 +3499,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="5"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -4054,7 +4028,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[A.xlsx]Data souce 2!PivotTable3</c:name>
+    <c:name>[Workshop week 4.xlsx]Data souce 2!PivotTable3</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -4127,19 +4101,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="5"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -4195,19 +4157,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="5"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -9697,7 +9647,93 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E173335D-1C30-4820-A2C9-20536E22E739}" name="PivotTable2" cacheId="1296" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EE0205F0-7B0B-4F5B-B634-EB22D7311CF5}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="20">
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Sale_Price" fld="6" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E173335D-1C30-4820-A2C9-20536E22E739}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="2">
   <location ref="F3:H20" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="20">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -9934,94 +9970,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EE0205F0-7B0B-4F5B-B634-EB22D7311CF5}" name="PivotTable1" cacheId="1296" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
-  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="20">
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="6">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Sale_Price" fld="6" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6904D0C9-0C76-478B-923B-D680A6A0928F}" name="PivotTable3" cacheId="1296" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6904D0C9-0C76-478B-923B-D680A6A0928F}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:C8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="20">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -10121,7 +10071,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1DEDDD77-A1E2-40AC-B0D6-2CD39587FBD7}" name="PivotTable5" cacheId="1296" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1DEDDD77-A1E2-40AC-B0D6-2CD39587FBD7}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
   <location ref="F153:G159" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="20">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -10217,7 +10167,7 @@
     <tableColumn id="5" xr3:uid="{8D332753-1820-4AAC-813F-54C82816523D}" name="Vehicle_Sub_Category"/>
     <tableColumn id="6" xr3:uid="{7B9A3D3C-62AC-4C59-AA48-358AD8D5498F}" name="Market_Segment"/>
     <tableColumn id="7" xr3:uid="{B550C13B-034B-44F7-B07D-7F72466DCFF2}" name="Sale_Price"/>
-    <tableColumn id="8" xr3:uid="{76137164-A8FC-4DD9-9B95-0FE0DCBCD02C}" name="Column1" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{76137164-A8FC-4DD9-9B95-0FE0DCBCD02C}" name="Column1" dataDxfId="1"/>
     <tableColumn id="9" xr3:uid="{71119990-5767-4143-A46E-91D9E58B1AA1}" name="Customer_Name"/>
     <tableColumn id="10" xr3:uid="{656E8C6F-DDC1-4CD2-B764-870DA55007D8}" name="Customer_Email"/>
     <tableColumn id="11" xr3:uid="{82BE8A9F-5A46-4640-8C11-2B599CFBCC54}" name="Dealer_Name"/>
@@ -10549,38 +10499,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D207786-3359-4486-8CA0-F0F0DC9D8567}">
-  <dimension ref="A3:L20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A3:H20"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:12">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:8">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>3</v>
       </c>
       <c r="H3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4">
         <v>1314901</v>
       </c>
       <c r="F4" t="s">
@@ -10589,58 +10539,57 @@
       <c r="G4" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="1">
+      <c r="H4">
         <v>185600</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5">
         <v>1553700</v>
       </c>
       <c r="G5" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5">
         <v>24500</v>
       </c>
-      <c r="L5" s="1"/>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6">
         <v>2433600</v>
       </c>
       <c r="G6" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6">
         <v>344500</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7">
         <v>652800</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7">
         <v>554600</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8">
         <v>199501</v>
       </c>
       <c r="F8" t="s">
@@ -10649,83 +10598,83 @@
       <c r="G8" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8">
         <v>358500</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9">
         <v>6154502</v>
       </c>
       <c r="G9" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9">
         <v>543801</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:8">
       <c r="G10" t="s">
         <v>18</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H10">
         <v>506300</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:8">
       <c r="F11" t="s">
         <v>19</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H11">
         <v>1408601</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:8">
       <c r="F12" t="s">
         <v>20</v>
       </c>
       <c r="G12" t="s">
         <v>21</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H12">
         <v>668701</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:8">
       <c r="G13" t="s">
         <v>22</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H13">
         <v>776500</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:8">
       <c r="G14" t="s">
         <v>23</v>
       </c>
-      <c r="H14" s="1">
+      <c r="H14">
         <v>564800</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:8">
       <c r="F15" t="s">
         <v>24</v>
       </c>
-      <c r="H15" s="1">
+      <c r="H15">
         <v>2010001</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:8">
       <c r="F16" t="s">
         <v>25</v>
       </c>
       <c r="G16" t="s">
         <v>26</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H16">
         <v>895000</v>
       </c>
     </row>
@@ -10733,7 +10682,7 @@
       <c r="G17" t="s">
         <v>27</v>
       </c>
-      <c r="H17" s="1">
+      <c r="H17">
         <v>763700</v>
       </c>
     </row>
@@ -10741,7 +10690,7 @@
       <c r="G18" t="s">
         <v>28</v>
       </c>
-      <c r="H18" s="1">
+      <c r="H18">
         <v>522600</v>
       </c>
     </row>
@@ -10749,7 +10698,7 @@
       <c r="F19" t="s">
         <v>29</v>
       </c>
-      <c r="H19" s="1">
+      <c r="H19">
         <v>2181300</v>
       </c>
     </row>
@@ -10757,7 +10706,7 @@
       <c r="F20" t="s">
         <v>16</v>
       </c>
-      <c r="H20" s="1">
+      <c r="H20">
         <v>6154502</v>
       </c>
     </row>
@@ -10770,15 +10719,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FB383C1-C284-431D-B4B8-8B91FA714436}">
   <dimension ref="A3:C8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B3" t="s">
@@ -10792,10 +10741,10 @@
       <c r="A4" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4">
         <v>31</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4">
         <v>31</v>
       </c>
     </row>
@@ -10803,10 +10752,10 @@
       <c r="A5" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5">
         <v>29</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5">
         <v>29</v>
       </c>
     </row>
@@ -10814,10 +10763,10 @@
       <c r="A6" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6">
         <v>30</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6">
         <v>30</v>
       </c>
     </row>
@@ -10825,10 +10774,10 @@
       <c r="A7" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7">
         <v>46</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7">
         <v>46</v>
       </c>
     </row>
@@ -10836,10 +10785,10 @@
       <c r="A8" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8">
         <v>136</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8">
         <v>136</v>
       </c>
     </row>
@@ -10852,27 +10801,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{555FA8E6-3421-4302-957F-39B82C6F0E09}">
   <dimension ref="A1:T253"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.42578125" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.44140625" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="20.25" customHeight="1">
@@ -10897,7 +10846,7 @@
       <c r="G1" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>43</v>
       </c>
       <c r="I1" t="s">
@@ -10956,7 +10905,10 @@
       <c r="F2" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="G2">
+        <v>24500</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>58</v>
       </c>
       <c r="I2" t="s">
@@ -11018,7 +10970,7 @@
       <c r="G3">
         <v>24500</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>69</v>
       </c>
       <c r="I3" t="s">
@@ -11080,7 +11032,7 @@
       <c r="G4">
         <v>26800</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I4" t="s">
@@ -11142,7 +11094,7 @@
       <c r="G5">
         <v>22900</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="1" t="s">
         <v>58</v>
       </c>
       <c r="I5" t="s">
@@ -11204,7 +11156,7 @@
       <c r="G6">
         <v>29500</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I6" t="s">
@@ -11266,7 +11218,7 @@
       <c r="G7">
         <v>38900</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I7" t="s">
@@ -11328,7 +11280,7 @@
       <c r="G8">
         <v>42000</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="1" t="s">
         <v>113</v>
       </c>
       <c r="I8" t="s">
@@ -11390,7 +11342,7 @@
       <c r="G9">
         <v>25500</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I9" t="s">
@@ -11452,7 +11404,7 @@
       <c r="G10">
         <v>45900</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="1" t="s">
         <v>113</v>
       </c>
       <c r="I10" t="s">
@@ -11514,7 +11466,7 @@
       <c r="G11">
         <v>89500</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="1" t="s">
         <v>134</v>
       </c>
       <c r="I11" t="s">
@@ -11573,7 +11525,7 @@
       <c r="G12">
         <v>28900</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I12" t="s">
@@ -11635,7 +11587,7 @@
       <c r="G13">
         <v>31200</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I13" t="s">
@@ -11697,7 +11649,7 @@
       <c r="G14">
         <v>27500</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I14" t="s">
@@ -11759,7 +11711,7 @@
       <c r="G15">
         <v>35800</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H15" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I15" t="s">
@@ -11821,7 +11773,7 @@
       <c r="G16">
         <v>41200</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="H16" s="1" t="s">
         <v>113</v>
       </c>
       <c r="I16" t="s">
@@ -11883,7 +11835,7 @@
       <c r="G17">
         <v>44500</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" s="1" t="s">
         <v>113</v>
       </c>
       <c r="I17" t="s">
@@ -11945,7 +11897,7 @@
       <c r="G18">
         <v>24800</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="H18" s="1" t="s">
         <v>58</v>
       </c>
       <c r="I18" t="s">
@@ -12007,7 +11959,7 @@
       <c r="G19">
         <v>59900</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="H19" s="1" t="s">
         <v>113</v>
       </c>
       <c r="I19" t="s">
@@ -12069,7 +12021,7 @@
       <c r="G20">
         <v>52900</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="H20" s="1" t="s">
         <v>113</v>
       </c>
       <c r="I20" t="s">
@@ -12128,7 +12080,7 @@
       <c r="G21">
         <v>29800</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="H21" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I21" t="s">
@@ -12190,7 +12142,7 @@
       <c r="G22">
         <v>29500</v>
       </c>
-      <c r="H22" s="2" t="s">
+      <c r="H22" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I22" t="s">
@@ -12252,7 +12204,7 @@
       <c r="G23">
         <v>24500</v>
       </c>
-      <c r="H23" s="2" t="s">
+      <c r="H23" s="1" t="s">
         <v>58</v>
       </c>
       <c r="I23" t="s">
@@ -12314,7 +12266,7 @@
       <c r="G24">
         <v>32500</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="H24" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I24" t="s">
@@ -12376,7 +12328,7 @@
       <c r="G25">
         <v>38900</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="H25" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I25" t="s">
@@ -12438,7 +12390,7 @@
       <c r="G26">
         <v>36800</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="H26" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I26" t="s">
@@ -12500,7 +12452,7 @@
       <c r="G27">
         <v>28900</v>
       </c>
-      <c r="H27" s="2" t="s">
+      <c r="H27" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I27" t="s">
@@ -12562,7 +12514,7 @@
       <c r="G28">
         <v>42900</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="H28" s="1" t="s">
         <v>113</v>
       </c>
       <c r="I28" t="s">
@@ -12624,7 +12576,7 @@
       <c r="G29">
         <v>58900</v>
       </c>
-      <c r="H29" s="2" t="s">
+      <c r="H29" s="1" t="s">
         <v>113</v>
       </c>
       <c r="I29" t="s">
@@ -12683,7 +12635,7 @@
       <c r="G30">
         <v>33500</v>
       </c>
-      <c r="H30" s="2" t="s">
+      <c r="H30" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I30" t="s">
@@ -12745,7 +12697,7 @@
       <c r="G31">
         <v>35800</v>
       </c>
-      <c r="H31" s="2" t="s">
+      <c r="H31" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I31" t="s">
@@ -12807,7 +12759,7 @@
       <c r="G32">
         <v>29800</v>
       </c>
-      <c r="H32" s="2" t="s">
+      <c r="H32" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I32" t="s">
@@ -12869,7 +12821,7 @@
       <c r="G33">
         <v>26500</v>
       </c>
-      <c r="H33" s="2" t="s">
+      <c r="H33" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I33" t="s">
@@ -12931,7 +12883,7 @@
       <c r="G34">
         <v>27900</v>
       </c>
-      <c r="H34" s="2" t="s">
+      <c r="H34" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I34" t="s">
@@ -12993,7 +12945,7 @@
       <c r="G35">
         <v>30200</v>
       </c>
-      <c r="H35" s="2" t="s">
+      <c r="H35" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I35" t="s">
@@ -13055,7 +13007,7 @@
       <c r="G36">
         <v>39500</v>
       </c>
-      <c r="H36" s="2" t="s">
+      <c r="H36" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I36" t="s">
@@ -13117,7 +13069,7 @@
       <c r="G37">
         <v>38900</v>
       </c>
-      <c r="H37" s="2" t="s">
+      <c r="H37" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I37" t="s">
@@ -13179,7 +13131,7 @@
       <c r="G38">
         <v>99900</v>
       </c>
-      <c r="H38" s="2" t="s">
+      <c r="H38" s="1" t="s">
         <v>247</v>
       </c>
       <c r="I38" t="s">
@@ -13238,7 +13190,7 @@
       <c r="G39">
         <v>42500</v>
       </c>
-      <c r="H39" s="2" t="s">
+      <c r="H39" s="1" t="s">
         <v>113</v>
       </c>
       <c r="I39" t="s">
@@ -13300,7 +13252,7 @@
       <c r="G40">
         <v>44800</v>
       </c>
-      <c r="H40" s="2" t="s">
+      <c r="H40" s="1" t="s">
         <v>113</v>
       </c>
       <c r="I40" t="s">
@@ -13362,7 +13314,7 @@
       <c r="G41">
         <v>34500</v>
       </c>
-      <c r="H41" s="2" t="s">
+      <c r="H41" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I41" t="s">
@@ -13424,7 +13376,7 @@
       <c r="G42">
         <v>48900</v>
       </c>
-      <c r="H42" s="2" t="s">
+      <c r="H42" s="1" t="s">
         <v>113</v>
       </c>
       <c r="I42" t="s">
@@ -13486,7 +13438,7 @@
       <c r="G43">
         <v>31800</v>
       </c>
-      <c r="H43" s="2" t="s">
+      <c r="H43" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I43" t="s">
@@ -13548,7 +13500,7 @@
       <c r="G44">
         <v>35900</v>
       </c>
-      <c r="H44" s="2" t="s">
+      <c r="H44" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I44" t="s">
@@ -13610,7 +13562,7 @@
       <c r="G45">
         <v>35901</v>
       </c>
-      <c r="H45" s="2" t="s">
+      <c r="H45" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I45" t="s">
@@ -13672,7 +13624,7 @@
       <c r="G46">
         <v>49900</v>
       </c>
-      <c r="H46" s="2" t="s">
+      <c r="H46" s="1" t="s">
         <v>113</v>
       </c>
       <c r="I46" t="s">
@@ -13734,7 +13686,7 @@
       <c r="G47">
         <v>39800</v>
       </c>
-      <c r="H47" s="2" t="s">
+      <c r="H47" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I47" t="s">
@@ -13796,7 +13748,7 @@
       <c r="G48">
         <v>33500</v>
       </c>
-      <c r="H48" s="2" t="s">
+      <c r="H48" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I48" t="s">
@@ -13858,7 +13810,7 @@
       <c r="G49">
         <v>37900</v>
       </c>
-      <c r="H49" s="2" t="s">
+      <c r="H49" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I49" t="s">
@@ -13920,7 +13872,7 @@
       <c r="G50">
         <v>29800</v>
       </c>
-      <c r="H50" s="2" t="s">
+      <c r="H50" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I50" t="s">
@@ -13982,7 +13934,7 @@
       <c r="G51">
         <v>41200</v>
       </c>
-      <c r="H51" s="2" t="s">
+      <c r="H51" s="1" t="s">
         <v>113</v>
       </c>
       <c r="I51" t="s">
@@ -14044,7 +13996,7 @@
       <c r="G52">
         <v>79900</v>
       </c>
-      <c r="H52" s="2" t="s">
+      <c r="H52" s="1" t="s">
         <v>134</v>
       </c>
       <c r="I52" t="s">
@@ -14103,7 +14055,7 @@
       <c r="G53">
         <v>26900</v>
       </c>
-      <c r="H53" s="2" t="s">
+      <c r="H53" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I53" t="s">
@@ -14165,7 +14117,7 @@
       <c r="G54">
         <v>39500</v>
       </c>
-      <c r="H54" s="2" t="s">
+      <c r="H54" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I54" t="s">
@@ -14227,7 +14179,7 @@
       <c r="G55">
         <v>36800</v>
       </c>
-      <c r="H55" s="2" t="s">
+      <c r="H55" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I55" t="s">
@@ -14289,7 +14241,7 @@
       <c r="G56">
         <v>18900</v>
       </c>
-      <c r="H56" s="2" t="s">
+      <c r="H56" s="1" t="s">
         <v>58</v>
       </c>
       <c r="I56" t="s">
@@ -14351,7 +14303,7 @@
       <c r="G57">
         <v>43500</v>
       </c>
-      <c r="H57" s="2" t="s">
+      <c r="H57" s="1" t="s">
         <v>113</v>
       </c>
       <c r="I57" t="s">
@@ -14413,7 +14365,7 @@
       <c r="G58">
         <v>89900</v>
       </c>
-      <c r="H58" s="2" t="s">
+      <c r="H58" s="1" t="s">
         <v>134</v>
       </c>
       <c r="I58" t="s">
@@ -14475,7 +14427,7 @@
       <c r="G59">
         <v>129900</v>
       </c>
-      <c r="H59" s="2" t="s">
+      <c r="H59" s="1" t="s">
         <v>247</v>
       </c>
       <c r="I59" t="s">
@@ -14534,7 +14486,7 @@
       <c r="G60">
         <v>37800</v>
       </c>
-      <c r="H60" s="2" t="s">
+      <c r="H60" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I60" t="s">
@@ -14596,7 +14548,7 @@
       <c r="G61">
         <v>56900</v>
       </c>
-      <c r="H61" s="2" t="s">
+      <c r="H61" s="1" t="s">
         <v>113</v>
       </c>
       <c r="I61" t="s">
@@ -14658,7 +14610,7 @@
       <c r="G62">
         <v>51200</v>
       </c>
-      <c r="H62" s="2" t="s">
+      <c r="H62" s="1" t="s">
         <v>113</v>
       </c>
       <c r="I62" t="s">
@@ -14720,7 +14672,7 @@
       <c r="G63">
         <v>47500</v>
       </c>
-      <c r="H63" s="2" t="s">
+      <c r="H63" s="1" t="s">
         <v>113</v>
       </c>
       <c r="I63" t="s">
@@ -14782,7 +14734,7 @@
       <c r="G64">
         <v>38900</v>
       </c>
-      <c r="H64" s="2" t="s">
+      <c r="H64" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I64" t="s">
@@ -14844,7 +14796,7 @@
       <c r="G65">
         <v>58900</v>
       </c>
-      <c r="H65" s="2" t="s">
+      <c r="H65" s="1" t="s">
         <v>113</v>
       </c>
       <c r="I65" t="s">
@@ -14906,7 +14858,7 @@
       <c r="G66">
         <v>99900</v>
       </c>
-      <c r="H66" s="2" t="s">
+      <c r="H66" s="1" t="s">
         <v>247</v>
       </c>
       <c r="I66" t="s">
@@ -14968,7 +14920,7 @@
       <c r="G67">
         <v>35800</v>
       </c>
-      <c r="H67" s="2" t="s">
+      <c r="H67" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I67" t="s">
@@ -15030,7 +14982,7 @@
       <c r="G68">
         <v>39500</v>
       </c>
-      <c r="H68" s="2" t="s">
+      <c r="H68" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I68" t="s">
@@ -15092,7 +15044,7 @@
       <c r="G69">
         <v>32900</v>
       </c>
-      <c r="H69" s="2" t="s">
+      <c r="H69" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I69" t="s">
@@ -15154,7 +15106,7 @@
       <c r="G70">
         <v>28900</v>
       </c>
-      <c r="H70" s="2" t="s">
+      <c r="H70" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I70" t="s">
@@ -15216,7 +15168,7 @@
       <c r="G71">
         <v>28901</v>
       </c>
-      <c r="H71" s="2" t="s">
+      <c r="H71" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I71" t="s">
@@ -15278,7 +15230,7 @@
       <c r="G72">
         <v>33500</v>
       </c>
-      <c r="H72" s="2" t="s">
+      <c r="H72" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I72" t="s">
@@ -15340,7 +15292,7 @@
       <c r="G73">
         <v>179900</v>
       </c>
-      <c r="H73" s="2" t="s">
+      <c r="H73" s="1" t="s">
         <v>399</v>
       </c>
       <c r="I73" t="s">
@@ -15399,7 +15351,7 @@
       <c r="G74">
         <v>24900</v>
       </c>
-      <c r="H74" s="2" t="s">
+      <c r="H74" s="1" t="s">
         <v>58</v>
       </c>
       <c r="I74" t="s">
@@ -15461,7 +15413,7 @@
       <c r="G75">
         <v>31500</v>
       </c>
-      <c r="H75" s="2" t="s">
+      <c r="H75" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I75" t="s">
@@ -15523,7 +15475,7 @@
       <c r="G76">
         <v>26900</v>
       </c>
-      <c r="H76" s="2" t="s">
+      <c r="H76" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I76" t="s">
@@ -15585,7 +15537,7 @@
       <c r="G77">
         <v>23500</v>
       </c>
-      <c r="H77" s="2" t="s">
+      <c r="H77" s="1" t="s">
         <v>58</v>
       </c>
       <c r="I77" t="s">
@@ -15647,7 +15599,7 @@
       <c r="G78">
         <v>22900</v>
       </c>
-      <c r="H78" s="2" t="s">
+      <c r="H78" s="1" t="s">
         <v>58</v>
       </c>
       <c r="I78" t="s">
@@ -15709,7 +15661,7 @@
       <c r="G79">
         <v>28900</v>
       </c>
-      <c r="H79" s="2" t="s">
+      <c r="H79" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I79" t="s">
@@ -15771,7 +15723,7 @@
       <c r="G80">
         <v>62900</v>
       </c>
-      <c r="H80" s="2" t="s">
+      <c r="H80" s="1" t="s">
         <v>134</v>
       </c>
       <c r="I80" t="s">
@@ -15833,7 +15785,7 @@
       <c r="G81">
         <v>39900</v>
       </c>
-      <c r="H81" s="2" t="s">
+      <c r="H81" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I81" t="s">
@@ -15892,7 +15844,7 @@
       <c r="G82">
         <v>27900</v>
       </c>
-      <c r="H82" s="2" t="s">
+      <c r="H82" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I82" t="s">
@@ -15954,7 +15906,7 @@
       <c r="G83">
         <v>35800</v>
       </c>
-      <c r="H83" s="2" t="s">
+      <c r="H83" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I83" t="s">
@@ -16016,7 +15968,7 @@
       <c r="G84">
         <v>38500</v>
       </c>
-      <c r="H84" s="2" t="s">
+      <c r="H84" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I84" t="s">
@@ -16078,7 +16030,7 @@
       <c r="G85">
         <v>29800</v>
       </c>
-      <c r="H85" s="2" t="s">
+      <c r="H85" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I85" t="s">
@@ -16140,7 +16092,7 @@
       <c r="G86">
         <v>21900</v>
       </c>
-      <c r="H86" s="2" t="s">
+      <c r="H86" s="1" t="s">
         <v>58</v>
       </c>
       <c r="I86" t="s">
@@ -16202,7 +16154,7 @@
       <c r="G87">
         <v>32500</v>
       </c>
-      <c r="H87" s="2" t="s">
+      <c r="H87" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I87" t="s">
@@ -16264,7 +16216,7 @@
       <c r="G88">
         <v>35200</v>
       </c>
-      <c r="H88" s="2" t="s">
+      <c r="H88" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I88" t="s">
@@ -16326,7 +16278,7 @@
       <c r="G89">
         <v>74900</v>
       </c>
-      <c r="H89" s="2" t="s">
+      <c r="H89" s="1" t="s">
         <v>134</v>
       </c>
       <c r="I89" t="s">
@@ -16385,7 +16337,7 @@
       <c r="G90">
         <v>19900</v>
       </c>
-      <c r="H90" s="2" t="s">
+      <c r="H90" s="1" t="s">
         <v>58</v>
       </c>
       <c r="I90" t="s">
@@ -16447,7 +16399,7 @@
       <c r="G91">
         <v>18500</v>
       </c>
-      <c r="H91" s="2" t="s">
+      <c r="H91" s="1" t="s">
         <v>58</v>
       </c>
       <c r="I91" t="s">
@@ -16509,7 +16461,7 @@
       <c r="G92">
         <v>17800</v>
       </c>
-      <c r="H92" s="2" t="s">
+      <c r="H92" s="1" t="s">
         <v>58</v>
       </c>
       <c r="I92" t="s">
@@ -16571,7 +16523,7 @@
       <c r="G93">
         <v>23900</v>
       </c>
-      <c r="H93" s="2" t="s">
+      <c r="H93" s="1" t="s">
         <v>58</v>
       </c>
       <c r="I93" t="s">
@@ -16633,7 +16585,7 @@
       <c r="G94">
         <v>26800</v>
       </c>
-      <c r="H94" s="2" t="s">
+      <c r="H94" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I94" t="s">
@@ -16695,7 +16647,7 @@
       <c r="G95">
         <v>22900</v>
       </c>
-      <c r="H95" s="2" t="s">
+      <c r="H95" s="1" t="s">
         <v>58</v>
       </c>
       <c r="I95" t="s">
@@ -16757,7 +16709,7 @@
       <c r="G96">
         <v>16500</v>
       </c>
-      <c r="H96" s="2" t="s">
+      <c r="H96" s="1" t="s">
         <v>58</v>
       </c>
       <c r="I96" t="s">
@@ -16819,7 +16771,7 @@
       <c r="G97">
         <v>149900</v>
       </c>
-      <c r="H97" s="2" t="s">
+      <c r="H97" s="1" t="s">
         <v>399</v>
       </c>
       <c r="I97" t="s">
@@ -16881,7 +16833,7 @@
       <c r="G98">
         <v>24900</v>
       </c>
-      <c r="H98" s="2" t="s">
+      <c r="H98" s="1" t="s">
         <v>58</v>
       </c>
       <c r="I98" t="s">
@@ -16943,7 +16895,7 @@
       <c r="G99">
         <v>26500</v>
       </c>
-      <c r="H99" s="2" t="s">
+      <c r="H99" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I99" t="s">
@@ -17005,7 +16957,7 @@
       <c r="G100">
         <v>21800</v>
       </c>
-      <c r="H100" s="2" t="s">
+      <c r="H100" s="1" t="s">
         <v>58</v>
       </c>
       <c r="I100" t="s">
@@ -17067,7 +17019,7 @@
       <c r="G101">
         <v>24500</v>
       </c>
-      <c r="H101" s="2" t="s">
+      <c r="H101" s="1" t="s">
         <v>58</v>
       </c>
       <c r="I101" t="s">
@@ -17129,7 +17081,7 @@
       <c r="G102">
         <v>27900</v>
       </c>
-      <c r="H102" s="2" t="s">
+      <c r="H102" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I102" t="s">
@@ -17191,7 +17143,7 @@
       <c r="G103">
         <v>23900</v>
       </c>
-      <c r="H103" s="2" t="s">
+      <c r="H103" s="1" t="s">
         <v>58</v>
       </c>
       <c r="I103" t="s">
@@ -17253,7 +17205,7 @@
       <c r="G104">
         <v>25800</v>
       </c>
-      <c r="H104" s="2" t="s">
+      <c r="H104" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I104" t="s">
@@ -17315,7 +17267,7 @@
       <c r="G105">
         <v>64900</v>
       </c>
-      <c r="H105" s="2" t="s">
+      <c r="H105" s="1" t="s">
         <v>134</v>
       </c>
       <c r="I105" t="s">
@@ -17374,7 +17326,7 @@
       <c r="G106">
         <v>33500</v>
       </c>
-      <c r="H106" s="2" t="s">
+      <c r="H106" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I106" t="s">
@@ -17436,7 +17388,7 @@
       <c r="G107">
         <v>58500</v>
       </c>
-      <c r="H107" s="2" t="s">
+      <c r="H107" s="1" t="s">
         <v>113</v>
       </c>
       <c r="I107" t="s">
@@ -17495,7 +17447,7 @@
       <c r="G108">
         <v>31900</v>
       </c>
-      <c r="H108" s="2" t="s">
+      <c r="H108" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I108" t="s">
@@ -17554,7 +17506,7 @@
       <c r="G109">
         <v>29800</v>
       </c>
-      <c r="H109" s="2" t="s">
+      <c r="H109" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I109" t="s">
@@ -17613,7 +17565,7 @@
       <c r="G110">
         <v>45900</v>
       </c>
-      <c r="H110" s="2" t="s">
+      <c r="H110" s="1" t="s">
         <v>113</v>
       </c>
       <c r="I110" t="s">
@@ -17675,7 +17627,7 @@
       <c r="G111">
         <v>55900</v>
       </c>
-      <c r="H111" s="2" t="s">
+      <c r="H111" s="1" t="s">
         <v>113</v>
       </c>
       <c r="I111" t="s">
@@ -17734,7 +17686,7 @@
       <c r="G112">
         <v>26900</v>
       </c>
-      <c r="H112" s="2" t="s">
+      <c r="H112" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I112" t="s">
@@ -17793,7 +17745,7 @@
       <c r="G113">
         <v>83900</v>
       </c>
-      <c r="H113" s="2" t="s">
+      <c r="H113" s="1" t="s">
         <v>134</v>
       </c>
       <c r="I113" t="s">
@@ -17852,7 +17804,7 @@
       <c r="G114">
         <v>47900</v>
       </c>
-      <c r="H114" s="2" t="s">
+      <c r="H114" s="1" t="s">
         <v>113</v>
       </c>
       <c r="I114" t="s">
@@ -17911,7 +17863,7 @@
       <c r="G115">
         <v>42500</v>
       </c>
-      <c r="H115" s="2" t="s">
+      <c r="H115" s="1" t="s">
         <v>113</v>
       </c>
       <c r="I115" t="s">
@@ -17970,7 +17922,7 @@
       <c r="G116">
         <v>43900</v>
       </c>
-      <c r="H116" s="2" t="s">
+      <c r="H116" s="1" t="s">
         <v>113</v>
       </c>
       <c r="I116" t="s">
@@ -18029,7 +17981,7 @@
       <c r="G117">
         <v>44500</v>
       </c>
-      <c r="H117" s="2" t="s">
+      <c r="H117" s="1" t="s">
         <v>113</v>
       </c>
       <c r="I117" t="s">
@@ -18088,7 +18040,7 @@
       <c r="G118">
         <v>47800</v>
       </c>
-      <c r="H118" s="2" t="s">
+      <c r="H118" s="1" t="s">
         <v>113</v>
       </c>
       <c r="I118" t="s">
@@ -18150,7 +18102,7 @@
       <c r="G119">
         <v>24900</v>
       </c>
-      <c r="H119" s="2" t="s">
+      <c r="H119" s="1" t="s">
         <v>58</v>
       </c>
       <c r="I119" t="s">
@@ -18212,7 +18164,7 @@
       <c r="G120">
         <v>65900</v>
       </c>
-      <c r="H120" s="2" t="s">
+      <c r="H120" s="1" t="s">
         <v>134</v>
       </c>
       <c r="I120" t="s">
@@ -18274,7 +18226,7 @@
       <c r="G121">
         <v>129900</v>
       </c>
-      <c r="H121" s="2" t="s">
+      <c r="H121" s="1" t="s">
         <v>247</v>
       </c>
       <c r="I121" t="s">
@@ -18333,7 +18285,7 @@
       <c r="G122">
         <v>32900</v>
       </c>
-      <c r="H122" s="2" t="s">
+      <c r="H122" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I122" t="s">
@@ -18395,7 +18347,7 @@
       <c r="G123">
         <v>31500</v>
       </c>
-      <c r="H123" s="2" t="s">
+      <c r="H123" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I123" t="s">
@@ -18457,7 +18409,7 @@
       <c r="G124">
         <v>41900</v>
       </c>
-      <c r="H124" s="2" t="s">
+      <c r="H124" s="1" t="s">
         <v>113</v>
       </c>
       <c r="I124" t="s">
@@ -18519,7 +18471,7 @@
       <c r="G125">
         <v>34500</v>
       </c>
-      <c r="H125" s="2" t="s">
+      <c r="H125" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I125" t="s">
@@ -18581,7 +18533,7 @@
       <c r="G126">
         <v>61900</v>
       </c>
-      <c r="H126" s="2" t="s">
+      <c r="H126" s="1" t="s">
         <v>134</v>
       </c>
       <c r="I126" t="s">
@@ -18643,7 +18595,7 @@
       <c r="G127">
         <v>29800</v>
       </c>
-      <c r="H127" s="2" t="s">
+      <c r="H127" s="1" t="s">
         <v>79</v>
       </c>
       <c r="I127" t="s">
@@ -18705,7 +18657,7 @@
       <c r="G128">
         <v>106900</v>
       </c>
-      <c r="H128" s="2" t="s">
+      <c r="H128" s="1" t="s">
         <v>247</v>
       </c>
       <c r="I128" t="s">
@@ -18767,7 +18719,7 @@
       <c r="G129">
         <v>69900</v>
       </c>
-      <c r="H129" s="2" t="s">
+      <c r="H129" s="1" t="s">
         <v>134</v>
       </c>
       <c r="I129" t="s">
@@ -18829,7 +18781,7 @@
       <c r="G130">
         <v>42900</v>
       </c>
-      <c r="H130" s="2" t="s">
+      <c r="H130" s="1" t="s">
         <v>113</v>
       </c>
       <c r="I130" t="s">
@@ -18891,7 +18843,7 @@
       <c r="G131">
         <v>51900</v>
       </c>
-      <c r="H131" s="2" t="s">
+      <c r="H131" s="1" t="s">
         <v>113</v>
       </c>
       <c r="I131" t="s">
@@ -18953,7 +18905,7 @@
       <c r="G132">
         <v>115900</v>
       </c>
-      <c r="H132" s="2" t="s">
+      <c r="H132" s="1" t="s">
         <v>247</v>
       </c>
       <c r="I132" t="s">
@@ -19015,7 +18967,7 @@
       <c r="G133">
         <v>74900</v>
       </c>
-      <c r="H133" s="2" t="s">
+      <c r="H133" s="1" t="s">
         <v>134</v>
       </c>
       <c r="I133" t="s">
@@ -19077,7 +19029,7 @@
       <c r="G134">
         <v>89900</v>
       </c>
-      <c r="H134" s="2" t="s">
+      <c r="H134" s="1" t="s">
         <v>134</v>
       </c>
       <c r="I134" t="s">
@@ -19139,7 +19091,7 @@
       <c r="G135">
         <v>79900</v>
       </c>
-      <c r="H135" s="2" t="s">
+      <c r="H135" s="1" t="s">
         <v>134</v>
       </c>
       <c r="I135" t="s">
@@ -19201,7 +19153,7 @@
       <c r="G136">
         <v>62900</v>
       </c>
-      <c r="H136" s="2" t="s">
+      <c r="H136" s="1" t="s">
         <v>134</v>
       </c>
       <c r="I136" t="s">
@@ -19263,7 +19215,7 @@
       <c r="G137">
         <v>199900</v>
       </c>
-      <c r="H137" s="2" t="s">
+      <c r="H137" s="1" t="s">
         <v>399</v>
       </c>
       <c r="I137" t="s">
@@ -19303,68 +19255,68 @@
     <row r="139" spans="1:20">
       <c r="G139">
         <f>SUM(Table13[Sale_Price])</f>
-        <v>6154502</v>
+        <v>6179002</v>
       </c>
     </row>
-    <row r="145" spans="3:9" ht="23.25">
-      <c r="C145" s="5" t="s">
+    <row r="145" spans="3:9" ht="23.4">
+      <c r="C145" s="4" t="s">
         <v>668</v>
       </c>
-      <c r="F145" s="12" t="s">
+      <c r="F145" s="10" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="146" spans="3:9" ht="18.75">
-      <c r="C146" s="4" t="s">
+    <row r="146" spans="3:9" ht="18">
+      <c r="C146" s="3" t="s">
         <v>670</v>
       </c>
-      <c r="F146" s="13" t="s">
+      <c r="F146" s="11" t="s">
         <v>671</v>
       </c>
       <c r="I146">
         <f>IF(B2="HONDA",AVERAGE(G2:G137))</f>
-        <v>45588.903703703705</v>
+        <v>45433.838235294119</v>
       </c>
     </row>
-    <row r="147" spans="3:9" ht="18.75">
-      <c r="C147" s="4" t="s">
+    <row r="147" spans="3:9" ht="18">
+      <c r="C147" s="3" t="s">
         <v>672</v>
       </c>
-      <c r="F147" s="14" t="s">
+      <c r="F147" s="12" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="148" spans="3:9" ht="36">
-      <c r="C148" s="4" t="s">
+    <row r="148" spans="3:9" ht="31.2">
+      <c r="C148" s="3" t="s">
         <v>674</v>
       </c>
-      <c r="F148" s="14" t="s">
+      <c r="F148" s="12" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="149" spans="3:9" ht="36">
-      <c r="C149" s="4" t="s">
+    <row r="149" spans="3:9" ht="18">
+      <c r="C149" s="3" t="s">
         <v>676</v>
       </c>
-      <c r="F149" s="14" t="s">
+      <c r="F149" s="12" t="s">
         <v>677</v>
       </c>
     </row>
     <row r="150" spans="3:9">
-      <c r="C150" s="3"/>
-      <c r="F150" s="13"/>
+      <c r="C150" s="2"/>
+      <c r="F150" s="11"/>
     </row>
     <row r="152" spans="3:9">
-      <c r="F152" s="9"/>
+      <c r="F152" s="8"/>
     </row>
     <row r="153" spans="3:9">
-      <c r="C153" s="7" t="s">
+      <c r="C153" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D153" s="7" t="s">
+      <c r="D153" s="6" t="s">
         <v>678</v>
       </c>
-      <c r="F153" s="6" t="s">
+      <c r="F153" s="5" t="s">
         <v>0</v>
       </c>
       <c r="G153" t="s">
@@ -19375,13 +19327,13 @@
       <c r="C154" t="s">
         <v>125</v>
       </c>
-      <c r="D154" s="1">
+      <c r="D154">
         <v>70081.818181818177</v>
       </c>
       <c r="F154" t="s">
         <v>4</v>
       </c>
-      <c r="G154" s="1">
+      <c r="G154">
         <v>1314901</v>
       </c>
     </row>
@@ -19389,13 +19341,13 @@
       <c r="C155" t="s">
         <v>119</v>
       </c>
-      <c r="D155" s="1">
+      <c r="D155">
         <v>43200.0625</v>
       </c>
       <c r="F155" t="s">
         <v>7</v>
       </c>
-      <c r="G155" s="1">
+      <c r="G155">
         <v>1553700</v>
       </c>
     </row>
@@ -19403,13 +19355,13 @@
       <c r="C156" t="s">
         <v>110</v>
       </c>
-      <c r="D156" s="1">
+      <c r="D156">
         <v>36606.3125</v>
       </c>
       <c r="F156" t="s">
         <v>9</v>
       </c>
-      <c r="G156" s="1">
+      <c r="G156">
         <v>2433600</v>
       </c>
     </row>
@@ -19417,13 +19369,13 @@
       <c r="C157" t="s">
         <v>54</v>
       </c>
-      <c r="D157" s="1">
+      <c r="D157">
         <v>33112.5</v>
       </c>
       <c r="F157" t="s">
         <v>11</v>
       </c>
-      <c r="G157" s="1">
+      <c r="G157">
         <v>652800</v>
       </c>
     </row>
@@ -19431,13 +19383,13 @@
       <c r="C158" t="s">
         <v>86</v>
       </c>
-      <c r="D158" s="1">
+      <c r="D158">
         <v>33929.411764705881</v>
       </c>
       <c r="F158" t="s">
         <v>13</v>
       </c>
-      <c r="G158" s="1">
+      <c r="G158">
         <v>199501</v>
       </c>
     </row>
@@ -19445,13 +19397,13 @@
       <c r="C159" t="s">
         <v>101</v>
       </c>
-      <c r="D159" s="1">
+      <c r="D159">
         <v>40514.285714285717</v>
       </c>
       <c r="F159" t="s">
         <v>16</v>
       </c>
-      <c r="G159" s="1">
+      <c r="G159">
         <v>6154502</v>
       </c>
     </row>
@@ -19459,7 +19411,7 @@
       <c r="C160" t="s">
         <v>76</v>
       </c>
-      <c r="D160" s="1">
+      <c r="D160">
         <v>37676.470588235294</v>
       </c>
     </row>
@@ -19467,7 +19419,7 @@
       <c r="C161" t="s">
         <v>132</v>
       </c>
-      <c r="D161" s="1">
+      <c r="D161">
         <v>105500</v>
       </c>
     </row>
@@ -19475,92 +19427,92 @@
       <c r="C162" t="s">
         <v>66</v>
       </c>
-      <c r="D162" s="1">
+      <c r="D162">
         <v>37170.588235294119</v>
       </c>
     </row>
     <row r="163" spans="3:5">
-      <c r="C163" s="10" t="s">
+      <c r="C163" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D163" s="11">
+      <c r="D163" s="9">
         <v>45588.903703703705</v>
       </c>
     </row>
-    <row r="168" spans="3:5" ht="15.75">
-      <c r="C168" s="15"/>
+    <row r="168" spans="3:5" ht="15.6">
+      <c r="C168" s="13"/>
     </row>
-    <row r="169" spans="3:5" ht="16.5">
-      <c r="C169" s="17" t="s">
+    <row r="169" spans="3:5" ht="15.6">
+      <c r="C169" s="15" t="s">
         <v>679</v>
       </c>
-      <c r="E169" s="16" t="s">
+      <c r="E169" s="14" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="170" spans="3:5" ht="16.5">
-      <c r="C170" s="18" t="s">
+    <row r="170" spans="3:5" ht="15.6">
+      <c r="C170" s="16" t="s">
         <v>681</v>
       </c>
-      <c r="E170" s="16" t="s">
+      <c r="E170" s="14" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="171" spans="3:5" ht="16.5">
-      <c r="C171" s="18" t="s">
+    <row r="171" spans="3:5" ht="15.6">
+      <c r="C171" s="16" t="s">
         <v>683</v>
       </c>
-      <c r="E171" s="16" t="s">
+      <c r="E171" s="14" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="172" spans="3:5" ht="32.25">
-      <c r="C172" s="18"/>
-      <c r="E172" s="16" t="s">
+    <row r="172" spans="3:5" ht="31.2">
+      <c r="C172" s="16"/>
+      <c r="E172" s="14" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="173" spans="3:5" ht="18.75">
-      <c r="C173" s="16" t="s">
+    <row r="173" spans="3:5" ht="18">
+      <c r="C173" s="14" t="s">
         <v>686</v>
       </c>
-      <c r="E173" s="8"/>
+      <c r="E173" s="7"/>
     </row>
-    <row r="174" spans="3:5" ht="18.75">
-      <c r="C174" s="16" t="s">
+    <row r="174" spans="3:5" ht="18">
+      <c r="C174" s="14" t="s">
         <v>687</v>
       </c>
-      <c r="E174" s="8"/>
+      <c r="E174" s="7"/>
     </row>
-    <row r="175" spans="3:5" ht="18.75">
-      <c r="C175" s="16" t="s">
+    <row r="175" spans="3:5" ht="18">
+      <c r="C175" s="14" t="s">
         <v>688</v>
       </c>
-      <c r="E175" s="8"/>
+      <c r="E175" s="7"/>
     </row>
-    <row r="176" spans="3:5" ht="15.75">
-      <c r="C176" s="17"/>
+    <row r="176" spans="3:5" ht="15.6">
+      <c r="C176" s="15"/>
     </row>
-    <row r="177" spans="3:3" ht="16.5">
-      <c r="C177" s="16" t="s">
+    <row r="177" spans="3:3" ht="15.6">
+      <c r="C177" s="14" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="178" spans="3:3" ht="16.5">
-      <c r="C178" s="16" t="s">
+    <row r="178" spans="3:3" ht="15.6">
+      <c r="C178" s="14" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="179" spans="3:3" ht="16.5">
-      <c r="C179" s="16" t="s">
+    <row r="179" spans="3:3" ht="15.6">
+      <c r="C179" s="14" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="180" spans="3:3" ht="15.75">
-      <c r="C180" s="15"/>
+    <row r="180" spans="3:3" ht="15.6">
+      <c r="C180" s="13"/>
     </row>
-    <row r="181" spans="3:3" ht="15.75">
-      <c r="C181" s="15"/>
+    <row r="181" spans="3:3" ht="15.6">
+      <c r="C181" s="13"/>
     </row>
     <row r="253" spans="1:1">
       <c r="A253">
@@ -19570,7 +19522,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:T137">
-    <cfRule type="containsBlanks" dxfId="1" priority="1">
+    <cfRule type="containsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(A2))=0</formula>
     </cfRule>
   </conditionalFormatting>
